--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/region-de-magallanes-y-de-la-antartica.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/region-de-magallanes-y-de-la-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5394-463-CM26</t>
+          <t>697-33-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,860 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>8121.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3866-35-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>69.251.300-2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>14255.77</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1609-76-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>72.229.800-4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>40815.81</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2363-34-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69.250.200-0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>9169.690000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3595-113-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.251.400-9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>8037.02</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2348-1322-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.250.200-0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>11996.39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1109692-128-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>62.000.760-9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>22786.12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1233613-826-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.980.960-2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Magallanes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>COMERCIAL FELP SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.427.199-8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>18754.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3866-73-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.251.300-2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>2368.03</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2348-1409-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.250.200-0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>33587.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1233613-1069-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.980.960-2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Magallanes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>11925.56</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1237328-241-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>70.931.900-0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>11134.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1237328-336-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>70.931.900-0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>33870.87</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3595-483-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.251.400-9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>9263.67</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5394-463-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>71.133.700-8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
         <v>27006.51</v>
       </c>
     </row>
